--- a/src/s3dgraphy/templates/em_data_template.xlsx
+++ b/src/s3dgraphy/templates/em_data_template.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>DOCUMENT_1</t>
+          <t>SOURCE_1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>DOCUMENT_2</t>
+          <t>SOURCE_2</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
